--- a/artfynd/A 52668-2025 artfynd.xlsx
+++ b/artfynd/A 52668-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129758004</v>
       </c>
       <c r="B2" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129757983</v>
       </c>
       <c r="B6" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>129758446</v>
       </c>
       <c r="B7" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>129757995</v>
       </c>
       <c r="B8" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129757960</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>129757977</v>
       </c>
       <c r="B10" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129758030</v>
+        <v>129757980</v>
       </c>
       <c r="B11" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,31 +1637,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1669,13 +1664,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493048</v>
+        <v>492985</v>
       </c>
       <c r="R11" t="n">
-        <v>6805900</v>
+        <v>6806054</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1707,12 +1702,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>flera</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1731,10 +1732,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129757980</v>
+        <v>129758030</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,26 +1743,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1769,13 +1775,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492985</v>
+        <v>493048</v>
       </c>
       <c r="R12" t="n">
-        <v>6806054</v>
+        <v>6805900</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1807,18 +1813,12 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>flera</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>129758420</v>
       </c>
       <c r="B13" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>129757969</v>
       </c>
       <c r="B14" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>129757954</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>129758041</v>
       </c>
       <c r="B16" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 52668-2025 artfynd.xlsx
+++ b/artfynd/A 52668-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129758004</v>
       </c>
       <c r="B2" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129757983</v>
       </c>
       <c r="B6" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>129758446</v>
       </c>
       <c r="B7" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
         <v>129757995</v>
       </c>
       <c r="B8" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129757960</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,32 +1525,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129757977</v>
+        <v>129757980</v>
       </c>
       <c r="B10" t="n">
-        <v>80141</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,6 +1601,11 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>flera</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1626,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129757980</v>
+        <v>129758030</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,26 +1642,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1664,13 +1674,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492985</v>
+        <v>493048</v>
       </c>
       <c r="R11" t="n">
-        <v>6806054</v>
+        <v>6805900</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1702,18 +1712,12 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>flera</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1732,42 +1736,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129758030</v>
+        <v>129757977</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1775,13 +1774,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493048</v>
+        <v>492985</v>
       </c>
       <c r="R12" t="n">
-        <v>6805900</v>
+        <v>6806054</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1819,6 +1818,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>129758420</v>
       </c>
       <c r="B13" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129757954</v>
+        <v>129758041</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,26 +2064,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2091,13 +2096,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493119</v>
+        <v>493066</v>
       </c>
       <c r="R15" t="n">
-        <v>6806129</v>
+        <v>6806071</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2135,7 +2140,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2154,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129758041</v>
+        <v>129757954</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,31 +2169,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2197,13 +2196,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493066</v>
+        <v>493119</v>
       </c>
       <c r="R16" t="n">
-        <v>6806071</v>
+        <v>6806129</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,6 +2240,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52668-2025 artfynd.xlsx
+++ b/artfynd/A 52668-2025 artfynd.xlsx
@@ -1307,7 +1307,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1525,32 +1525,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129757980</v>
+        <v>129757977</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,11 +1601,6 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>flera</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1736,32 +1731,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129757977</v>
+        <v>129757980</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,6 +1805,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>flera</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 52668-2025 artfynd.xlsx
+++ b/artfynd/A 52668-2025 artfynd.xlsx
@@ -1307,7 +1307,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1525,32 +1525,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129757977</v>
+        <v>129757980</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,6 +1601,11 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>flera</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1731,32 +1736,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129757980</v>
+        <v>129757977</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,11 +1812,6 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>flera</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129758041</v>
+        <v>129757954</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,31 +2064,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2096,13 +2091,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493066</v>
+        <v>493119</v>
       </c>
       <c r="R15" t="n">
-        <v>6806071</v>
+        <v>6806129</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2140,6 +2135,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2158,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129757954</v>
+        <v>129758041</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,26 +2165,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2196,13 +2197,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493119</v>
+        <v>493066</v>
       </c>
       <c r="R16" t="n">
-        <v>6806129</v>
+        <v>6806071</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2240,7 +2241,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52668-2025 artfynd.xlsx
+++ b/artfynd/A 52668-2025 artfynd.xlsx
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129757954</v>
+        <v>129758041</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,26 +2064,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2091,13 +2096,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493119</v>
+        <v>493066</v>
       </c>
       <c r="R15" t="n">
-        <v>6806129</v>
+        <v>6806071</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2135,7 +2140,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2154,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129758041</v>
+        <v>129757954</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,31 +2169,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2197,13 +2196,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493066</v>
+        <v>493119</v>
       </c>
       <c r="R16" t="n">
-        <v>6806071</v>
+        <v>6806129</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,6 +2240,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52668-2025 artfynd.xlsx
+++ b/artfynd/A 52668-2025 artfynd.xlsx
@@ -1307,7 +1307,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
         <v>129757995</v>
       </c>
       <c r="B8" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52668-2025 artfynd.xlsx
+++ b/artfynd/A 52668-2025 artfynd.xlsx
@@ -1317,7 +1317,7 @@
         <v>129757995</v>
       </c>
       <c r="B8" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1525,32 +1525,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129757980</v>
+        <v>129757977</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,11 +1601,6 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>flera</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1631,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129758030</v>
+        <v>129757980</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1642,31 +1637,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1674,13 +1664,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493048</v>
+        <v>492985</v>
       </c>
       <c r="R11" t="n">
-        <v>6805900</v>
+        <v>6806054</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1712,12 +1702,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>flera</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1736,37 +1732,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129757977</v>
+        <v>129758030</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1774,13 +1775,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492985</v>
+        <v>493048</v>
       </c>
       <c r="R12" t="n">
-        <v>6806054</v>
+        <v>6805900</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1818,7 +1819,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52668-2025 artfynd.xlsx
+++ b/artfynd/A 52668-2025 artfynd.xlsx
@@ -1525,37 +1525,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129757977</v>
+        <v>129758030</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1563,13 +1568,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492985</v>
+        <v>493048</v>
       </c>
       <c r="R10" t="n">
-        <v>6806054</v>
+        <v>6805900</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1607,7 +1612,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1732,42 +1736,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129758030</v>
+        <v>129757977</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1775,13 +1774,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493048</v>
+        <v>492985</v>
       </c>
       <c r="R12" t="n">
-        <v>6805900</v>
+        <v>6806054</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1819,6 +1818,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129758041</v>
+        <v>129757954</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,31 +2064,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2096,13 +2091,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493066</v>
+        <v>493119</v>
       </c>
       <c r="R15" t="n">
-        <v>6806071</v>
+        <v>6806129</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2140,6 +2135,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2158,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129757954</v>
+        <v>129758041</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,26 +2165,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2196,13 +2197,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493119</v>
+        <v>493066</v>
       </c>
       <c r="R16" t="n">
-        <v>6806129</v>
+        <v>6806071</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2240,7 +2241,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52668-2025 artfynd.xlsx
+++ b/artfynd/A 52668-2025 artfynd.xlsx
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129758030</v>
+        <v>129757980</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1536,31 +1536,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1568,13 +1563,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493048</v>
+        <v>492985</v>
       </c>
       <c r="R10" t="n">
-        <v>6805900</v>
+        <v>6806054</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,12 +1601,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>flera</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1630,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129757980</v>
+        <v>129758030</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,26 +1642,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1668,13 +1674,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492985</v>
+        <v>493048</v>
       </c>
       <c r="R11" t="n">
-        <v>6806054</v>
+        <v>6805900</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1706,18 +1712,12 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>flera</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129758041</v>
+        <v>129757954</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,31 +2064,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2096,13 +2091,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493066</v>
+        <v>493119</v>
       </c>
       <c r="R15" t="n">
-        <v>6806071</v>
+        <v>6806129</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2140,6 +2135,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2158,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129757954</v>
+        <v>129758041</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,26 +2165,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2196,13 +2197,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493119</v>
+        <v>493066</v>
       </c>
       <c r="R16" t="n">
-        <v>6806129</v>
+        <v>6806071</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2240,7 +2241,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52668-2025 artfynd.xlsx
+++ b/artfynd/A 52668-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129758004</v>
       </c>
       <c r="B2" t="n">
-        <v>79113</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129757983</v>
       </c>
       <c r="B6" t="n">
-        <v>79113</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>129758446</v>
       </c>
       <c r="B7" t="n">
-        <v>79113</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>129757995</v>
       </c>
       <c r="B8" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129757960</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>129757980</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>129758030</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>129757977</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>129758420</v>
       </c>
       <c r="B13" t="n">
-        <v>79113</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>129757969</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129757954</v>
+        <v>129758041</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,26 +2064,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2091,13 +2096,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493119</v>
+        <v>493066</v>
       </c>
       <c r="R15" t="n">
-        <v>6806129</v>
+        <v>6806071</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2135,7 +2140,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2154,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129758041</v>
+        <v>129757954</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,31 +2169,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2197,13 +2196,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493066</v>
+        <v>493119</v>
       </c>
       <c r="R16" t="n">
-        <v>6806071</v>
+        <v>6806129</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,6 +2240,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52668-2025 artfynd.xlsx
+++ b/artfynd/A 52668-2025 artfynd.xlsx
@@ -675,37 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129758004</v>
+        <v>129757984</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>5177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493059</v>
+        <v>493002</v>
       </c>
       <c r="R2" t="n">
-        <v>6806014</v>
+        <v>6806043</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -749,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>i samma träd  skinn av en järv !</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,43 +782,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129757984</v>
+        <v>129758004</v>
       </c>
       <c r="B3" t="n">
-        <v>5177</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493002</v>
+        <v>493059</v>
       </c>
       <c r="R3" t="n">
-        <v>6806043</v>
+        <v>6806014</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -861,6 +856,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>i samma träd  skinn av en järv !</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129757980</v>
+        <v>129758030</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1536,26 +1536,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1563,13 +1568,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492985</v>
+        <v>493048</v>
       </c>
       <c r="R10" t="n">
-        <v>6806054</v>
+        <v>6805900</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,18 +1606,12 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>flera</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1631,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129758030</v>
+        <v>129757980</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1642,31 +1641,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1674,13 +1668,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493048</v>
+        <v>492985</v>
       </c>
       <c r="R11" t="n">
-        <v>6805900</v>
+        <v>6806054</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1712,12 +1706,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>flera</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52668-2025 artfynd.xlsx
+++ b/artfynd/A 52668-2025 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129757984</v>
+        <v>129758004</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>79119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493002</v>
+        <v>493059</v>
       </c>
       <c r="R2" t="n">
-        <v>6806043</v>
+        <v>6806014</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -755,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>i samma träd  skinn av en järv !</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +781,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129758004</v>
+        <v>129757984</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>5177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493059</v>
+        <v>493002</v>
       </c>
       <c r="R3" t="n">
-        <v>6806014</v>
+        <v>6806043</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -856,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>i samma träd  skinn av en järv !</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1110,7 +1110,7 @@
         <v>129757983</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79119</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>129758446</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79119</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>129757995</v>
       </c>
       <c r="B8" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129757960</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>129758030</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>129757980</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>129757977</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>80152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>129758420</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>79119</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>129757969</v>
       </c>
       <c r="B14" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>129758041</v>
       </c>
       <c r="B15" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>129757954</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 52668-2025 artfynd.xlsx
+++ b/artfynd/A 52668-2025 artfynd.xlsx
@@ -1525,42 +1525,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129758030</v>
+        <v>129757977</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>80152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1568,13 +1563,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493048</v>
+        <v>492985</v>
       </c>
       <c r="R10" t="n">
-        <v>6805900</v>
+        <v>6806054</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1612,6 +1607,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1630,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129757980</v>
+        <v>129758030</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,26 +1637,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1668,13 +1669,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492985</v>
+        <v>493048</v>
       </c>
       <c r="R11" t="n">
-        <v>6806054</v>
+        <v>6805900</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1706,18 +1707,12 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>flera</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1736,32 +1731,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129757977</v>
+        <v>129757980</v>
       </c>
       <c r="B12" t="n">
-        <v>80152</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,6 +1805,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>flera</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 52668-2025 artfynd.xlsx
+++ b/artfynd/A 52668-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129758004</v>
       </c>
       <c r="B2" t="n">
-        <v>79119</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129757983</v>
       </c>
       <c r="B6" t="n">
-        <v>79119</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>129758446</v>
       </c>
       <c r="B7" t="n">
-        <v>79119</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>129757995</v>
       </c>
       <c r="B8" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129757960</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,32 +1525,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129757977</v>
+        <v>129757980</v>
       </c>
       <c r="B10" t="n">
-        <v>80152</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,6 +1601,11 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>flera</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1731,32 +1736,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129757980</v>
+        <v>129757977</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>80153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,11 +1812,6 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>flera</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>129758420</v>
       </c>
       <c r="B13" t="n">
-        <v>79119</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129758041</v>
+        <v>129757954</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,31 +2064,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2096,13 +2091,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493066</v>
+        <v>493119</v>
       </c>
       <c r="R15" t="n">
-        <v>6806071</v>
+        <v>6806129</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2140,6 +2135,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2158,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129757954</v>
+        <v>129758041</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,26 +2165,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2196,13 +2197,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493119</v>
+        <v>493066</v>
       </c>
       <c r="R16" t="n">
-        <v>6806129</v>
+        <v>6806071</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2240,7 +2241,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52668-2025 artfynd.xlsx
+++ b/artfynd/A 52668-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129758004</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129757983</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>129758446</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>129757995</v>
       </c>
       <c r="B8" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129757960</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>129757980</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,42 +1631,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129758030</v>
+        <v>129757977</v>
       </c>
       <c r="B11" t="n">
-        <v>57740</v>
+        <v>80154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1674,13 +1669,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493048</v>
+        <v>492985</v>
       </c>
       <c r="R11" t="n">
-        <v>6805900</v>
+        <v>6806054</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,6 +1713,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1736,37 +1732,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129757977</v>
+        <v>129758030</v>
       </c>
       <c r="B12" t="n">
-        <v>80153</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1774,13 +1775,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492985</v>
+        <v>493048</v>
       </c>
       <c r="R12" t="n">
-        <v>6806054</v>
+        <v>6805900</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1818,7 +1819,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>129758420</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>129757954</v>
       </c>
       <c r="B15" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
